--- a/data/trans_bre/P1421-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1421-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>215,09%</t>
+          <t>222,63%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,09</t>
+          <t>0,31; 4,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,31</t>
+          <t>-0,1; 4,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,22</t>
+          <t>-0,37; 2,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 12,15</t>
+          <t>2,15; 12,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 808,41</t>
+          <t>-7,06; 771,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 582,72</t>
+          <t>-19,21; 599,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 875,92</t>
+          <t>-41,75; 867,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,8; 883,17</t>
+          <t>12,16; 837,47</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>5,88</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>101,98%</t>
+          <t>128,06%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 8,03</t>
+          <t>3,3; 8,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,28</t>
+          <t>0,89; 4,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 8,4</t>
+          <t>3,98; 8,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 8,92</t>
+          <t>2,24; 9,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>97,72; 566,87</t>
+          <t>115,59; 607,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,87; 766,88</t>
+          <t>40,35; 640,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>243,18; 3640,16</t>
+          <t>251,54; 3551,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 305,83</t>
+          <t>28,58; 331,98</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>111,88%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,31</t>
+          <t>1,81; 6,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,54</t>
+          <t>3,12; 7,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,9</t>
+          <t>0,46; 3,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 7,94</t>
+          <t>2,82; 8,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,85; 436,58</t>
+          <t>60,84; 445,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>118,09; 852,47</t>
+          <t>102,9; 783,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 612,69</t>
+          <t>7,64; 711,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,57; 202,78</t>
+          <t>41,79; 244,1</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,01</t>
+          <t>8,38</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>216,06%</t>
+          <t>134,63%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,72</t>
+          <t>0,68; 5,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,9</t>
+          <t>2,57; 6,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,88</t>
+          <t>1,71; 5,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 14,69</t>
+          <t>5,27; 11,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,16; 297,96</t>
+          <t>15,55; 338,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>123,72; 1449,3</t>
+          <t>129,97; 1470,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,85; 546,16</t>
+          <t>53,06; 550,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93,38; 676,88</t>
+          <t>64,05; 240,84</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>8,14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>185,91%</t>
+          <t>194,24%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,22</t>
+          <t>-1,86; 4,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,45</t>
+          <t>1,87; 6,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,66</t>
+          <t>2,14; 7,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 10,47</t>
+          <t>5,43; 10,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 139,3</t>
+          <t>-31,16; 148,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,71; 2113,2</t>
+          <t>88,12; 1975,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,06; 585,79</t>
+          <t>50,28; 579,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>95,77; 346,85</t>
+          <t>90,69; 339,67</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>5,51</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>164,84%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,29</t>
+          <t>1,56; 7,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,58</t>
+          <t>2,78; 8,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,09</t>
+          <t>2,71; 8,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 6,06</t>
+          <t>3,14; 8,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,18; 599,11</t>
+          <t>22,06; 584,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>106,24; 2668,51</t>
+          <t>85,26; 2553,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>107,09; 2123,41</t>
+          <t>84,98; 2091,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,82; 196,08</t>
+          <t>63,51; 348,96</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>154,66%</t>
+          <t>157,51%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,69</t>
+          <t>-2,21; 3,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,06</t>
+          <t>2,89; 8,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,89</t>
+          <t>3,05; 10,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,36; 8,63</t>
+          <t>3,52; 8,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-61,01; 320,2</t>
+          <t>-57,31; 296,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,9; —</t>
+          <t>77,55; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,78; 880,14</t>
+          <t>61,98; 750,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,86; 318,21</t>
+          <t>60,61; 331,7</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,79</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>139,14%</t>
+          <t>149,38%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,37</t>
+          <t>2,45; 4,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,05</t>
+          <t>3,31; 5,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,04</t>
+          <t>3,15; 4,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,69</t>
+          <t>5,55; 7,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>86,9; 221,76</t>
+          <t>86,83; 214,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>223,98; 566,26</t>
+          <t>219,39; 524,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>184,12; 429,99</t>
+          <t>183,57; 449,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>89,21; 210,62</t>
+          <t>105,0; 201,19</t>
         </is>
       </c>
     </row>
